--- a/artfynd/A 10036-2026 artfynd.xlsx
+++ b/artfynd/A 10036-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>84259387</v>
+        <v>84259380</v>
       </c>
       <c r="B2" t="n">
-        <v>98563</v>
+        <v>99142</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220093</v>
+        <v>219847</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>84259398</v>
+        <v>84259387</v>
       </c>
       <c r="B3" t="n">
-        <v>97530</v>
+        <v>99022</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>220093</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>84259383</v>
+        <v>84259398</v>
       </c>
       <c r="B4" t="n">
-        <v>98669</v>
+        <v>97983</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222495</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Myggblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hammarbya paludosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Kuntze</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>84259386</v>
+        <v>84259382</v>
       </c>
       <c r="B5" t="n">
-        <v>98579</v>
+        <v>99140</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1019,19 +1019,23 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>223597</v>
+        <v>221952</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1115,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>84259380</v>
+        <v>84259362</v>
       </c>
       <c r="B6" t="n">
-        <v>98682</v>
+        <v>100143</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1126,21 +1130,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219847</v>
+        <v>222467</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Gräsull</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Eriophorum latifolium</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>Hoppe</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1226,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>84259382</v>
+        <v>84259383</v>
       </c>
       <c r="B7" t="n">
-        <v>98680</v>
+        <v>99128</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1237,21 +1241,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221952</v>
+        <v>222495</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Myggblomster</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hammarbya paludosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Kuntze</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1337,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>84259362</v>
+        <v>84259386</v>
       </c>
       <c r="B8" t="n">
-        <v>99674</v>
+        <v>99038</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1348,23 +1352,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222467</v>
+        <v>223597</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gräsull</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Eriophorum latifolium</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Hoppe</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>

--- a/artfynd/A 10036-2026 artfynd.xlsx
+++ b/artfynd/A 10036-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Hälsinglands flora (2019)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84259380</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Hälsinglands flora (2019)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84259387</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
           <t>Hälsinglands flora (2019)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84259398</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,6 +1136,11 @@
           <t>Hälsinglands flora (2019)</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84259382</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
           <t>Hälsinglands flora (2019)</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84259362</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1338,6 +1368,11 @@
           <t>Hälsinglands flora (2019)</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84259383</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1445,8 +1480,22 @@
           <t>Hälsinglands flora (2019)</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84259386</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>